--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486498_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486498_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7861</v>
+        <v>4.5294</v>
       </c>
       <c r="E2" t="n">
-        <v>2.343</v>
+        <v>3.2179</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4431</v>
+        <v>1.3115</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8218</v>
+        <v>5.6118</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0365</v>
+        <v>-0.3072</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8583</v>
+        <v>5.9191</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4354</v>
+        <v>6.1244</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2492</v>
+        <v>0.0611</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6846</v>
+        <v>6.0633</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3863</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2127</v>
+        <v>-0.3683</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1737</v>
+        <v>-0.1443</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2041</v>
+        <v>0.2226</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4747</v>
+        <v>-0.7739</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7295</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5204</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>V. ALVES BENITE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1132</v>
+        <v>4.1637</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7709</v>
+        <v>1.7573</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3423</v>
+        <v>2.4065</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6118</v>
+        <v>0.7851</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3072</v>
+        <v>-1.9282</v>
       </c>
       <c r="I3" t="n">
-        <v>5.9191</v>
+        <v>2.7133</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1244</v>
+        <v>1.2642</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0611</v>
+        <v>-1.7424</v>
       </c>
       <c r="L3" t="n">
-        <v>6.0633</v>
+        <v>3.0066</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.4791</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3683</v>
+        <v>-0.1858</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1443</v>
+        <v>-0.2933</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1936</v>
+        <v>0.2911</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2209</v>
+        <v>-0.6369</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0273</v>
+        <v>0.928</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
         <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. ALVES BENITE</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7475</v>
+        <v>3.9808</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3102</v>
+        <v>1.7842</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4373</v>
+        <v>2.1965</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7851</v>
+        <v>1.8218</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.9282</v>
+        <v>-0.0365</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7133</v>
+        <v>1.8583</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2642</v>
+        <v>1.4354</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.7424</v>
+        <v>-0.2492</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0066</v>
+        <v>1.6846</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4791</v>
+        <v>0.3863</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1858</v>
+        <v>0.2127</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2933</v>
+        <v>0.1737</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9576</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1251</v>
+        <v>1.3988</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0839</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9588</v>
+        <v>1.4829</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>0.7602</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.5204</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0781</v>
+        <v>2.2998</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6326</v>
+        <v>2.3516</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4455</v>
+        <v>-0.0517</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7416</v>
+        <v>3.6678</v>
       </c>
       <c r="H5" t="n">
-        <v>2.713</v>
+        <v>-1.4903</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0287</v>
+        <v>5.1581</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7347</v>
+        <v>3.1771</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5618</v>
+        <v>-1.1069</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1729</v>
+        <v>4.2839</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9931</v>
+        <v>0.4907</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8488</v>
+        <v>-0.3834</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1443</v>
+        <v>0.8741</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0553</v>
+        <v>-0.021</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3567</v>
+        <v>-0.2812</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6985</v>
+        <v>0.2602</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2838</v>
+        <v>-2.4345</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.2838</v>
+        <v>-0.5443</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7796</v>
+        <v>2.1647</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0163</v>
+        <v>0.6267</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2367</v>
+        <v>1.538</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6678</v>
+        <v>2.7416</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4903</v>
+        <v>2.713</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1581</v>
+        <v>0.0287</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1771</v>
+        <v>3.7347</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1069</v>
+        <v>3.5618</v>
       </c>
       <c r="L6" t="n">
-        <v>4.2839</v>
+        <v>0.1729</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4907</v>
+        <v>-0.9931</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3834</v>
+        <v>-0.8488</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8741</v>
+        <v>-0.1443</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5412</v>
+        <v>1.1419</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6165</v>
+        <v>0.3509</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0752</v>
+        <v>0.791</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.4345</v>
+        <v>-1.2838</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.5443</v>
+        <v>-1.2838</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0864</v>
+        <v>1.0556</v>
       </c>
       <c r="E7" t="n">
         <v>0.4664</v>
       </c>
       <c r="F7" t="n">
-        <v>0.62</v>
+        <v>0.5891</v>
       </c>
       <c r="G7" t="n">
         <v>2.2065</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0326</v>
+        <v>-0.0634</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2055</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1729</v>
+        <v>0.1421</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. STOLBETSKIY</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6906</v>
+        <v>0.7701</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.351</v>
+        <v>-0.3746</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0416</v>
+        <v>1.1446</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3035</v>
+        <v>-1.1443</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6175</v>
+        <v>-1.2591</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.314</v>
+        <v>0.1147</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5394</v>
+        <v>-0.4206</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3864</v>
+        <v>-0.9577</v>
       </c>
       <c r="L8" t="n">
-        <v>0.153</v>
+        <v>0.5371</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2359</v>
+        <v>-0.7237</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2311</v>
+        <v>-0.3013</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.467</v>
+        <v>-0.4224</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0396</v>
+        <v>0.7844</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1971</v>
+        <v>0.0036</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8425</v>
+        <v>0.7808</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>P. ALI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.616</v>
+        <v>0.6569</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3746</v>
+        <v>-0.1979</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9905</v>
+        <v>0.8548</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1443</v>
+        <v>0.3858</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2591</v>
+        <v>-1.1465</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1147</v>
+        <v>1.5323</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4206</v>
+        <v>0.7246</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9577</v>
+        <v>-0.6141</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5371</v>
+        <v>1.3387</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7237</v>
+        <v>-0.3388</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3013</v>
+        <v>-0.5324</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4224</v>
+        <v>0.1936</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6303</v>
+        <v>0.6636</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0036</v>
+        <v>0.1226</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6267</v>
+        <v>0.5411</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ALI</t>
+          <t>G. RENFROE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0171</v>
+        <v>0.1613</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8685</v>
+        <v>0.7902</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8856000000000001</v>
+        <v>-0.6289</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3858</v>
+        <v>0.0286</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1465</v>
+        <v>-0.2798</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5323</v>
+        <v>0.3084</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7246</v>
+        <v>0.8479</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6141</v>
+        <v>0.7331</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3387</v>
+        <v>0.1147</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3388</v>
+        <v>-0.8193</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5324</v>
+        <v>-1.0129</v>
       </c>
       <c r="O10" t="n">
         <v>0.1936</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0239</v>
+        <v>0.3927</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.548</v>
+        <v>-0.0577</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5719</v>
+        <v>0.4503</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ PASCUAL</t>
+          <t>D. STOLBETSKIY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0526</v>
+        <v>-0.0339</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9123</v>
+        <v>-0.7981</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8597</v>
+        <v>0.7642</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2598</v>
+        <v>0.3035</v>
       </c>
       <c r="H11" t="n">
-        <v>0.298</v>
+        <v>0.6175</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5578</v>
+        <v>-0.314</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7068</v>
+        <v>0.5394</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.3864</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7068</v>
+        <v>0.153</v>
       </c>
       <c r="M11" t="n">
-        <v>0.447</v>
+        <v>-0.2359</v>
       </c>
       <c r="N11" t="n">
-        <v>0.298</v>
+        <v>0.2311</v>
       </c>
       <c r="O11" t="n">
-        <v>0.149</v>
+        <v>-0.467</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2072</v>
+        <v>0.3151</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2055</v>
+        <v>-0.2499</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4127</v>
+        <v>0.5651</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. RENFROE</t>
+          <t>P. RODRIGUEZ PASCUAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5516</v>
+        <v>-0.2375</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2314</v>
+        <v>-0.9123</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.783</v>
+        <v>0.6748</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0286</v>
+        <v>-0.2598</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2798</v>
+        <v>0.298</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3084</v>
+        <v>-0.5578</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8479</v>
+        <v>-0.7068</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7331</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1147</v>
+        <v>-0.7068</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8193</v>
+        <v>0.447</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0129</v>
+        <v>0.298</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1936</v>
+        <v>0.149</v>
       </c>
       <c r="P12" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3203</v>
+        <v>0.0222</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6165</v>
+        <v>-0.2055</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2962</v>
+        <v>0.2277</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6858</v>
+        <v>-0.8863</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1507</v>
+        <v>-0.2963</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8365</v>
+        <v>-0.5899</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1158</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.43</v>
+        <v>0.2295</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2656</v>
+        <v>-0.1815</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1644</v>
+        <v>0.411</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1507,7 +1507,7 @@
         <v>8.415100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>10.2094</v>
+        <v>10.2095</v>
       </c>
       <c r="G14" t="n">
         <v>15.0326</v>
@@ -1522,10 +1522,10 @@
         <v>18.3649</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6365</v>
+        <v>-0.6365000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>19.00119999999999</v>
+        <v>19.0012</v>
       </c>
       <c r="M14" t="n">
         <v>-3.3324</v>
@@ -1534,7 +1534,7 @@
         <v>-2.5111</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8212</v>
+        <v>-0.8211999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>-1.0874</v>
@@ -1546,19 +1546,19 @@
         <v>10.8753</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3776</v>
+        <v>5.3775</v>
       </c>
       <c r="T14" t="n">
         <v>-2.1991</v>
       </c>
       <c r="U14" t="n">
-        <v>7.5766</v>
+        <v>7.576700000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6981000000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2123</v>
+        <v>4.212299999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-4.9104</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.84</v>
+        <v>1.1772</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4125</v>
+        <v>-0.0345</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4275</v>
+        <v>1.2118</v>
       </c>
       <c r="G15" t="n">
         <v>0.0263</v>
@@ -1624,13 +1624,13 @@
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0737</v>
+        <v>-0.5891</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0649</v>
+        <v>-0.5119</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1385</v>
+        <v>-0.0772</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.406</v>
+        <v>0.5486</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5334</v>
+        <v>0.6451</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1273</v>
+        <v>-0.0965</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1725</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.769</v>
+        <v>-0.6264</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5732</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0532</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3583</v>
+        <v>0.4379</v>
       </c>
       <c r="E17" t="n">
-        <v>3.286</v>
+        <v>3.0624</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.9277</v>
+        <v>-2.6245</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1573</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5942</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4879</v>
+        <v>-0.7114</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1064</v>
+        <v>0.1968</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3635</v>
+        <v>-1.3442</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2999</v>
+        <v>-2.1881</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9364</v>
+        <v>0.8439</v>
       </c>
       <c r="G18" t="n">
         <v>0.2448</v>
@@ -1858,13 +1858,13 @@
         <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3493</v>
+        <v>0.3686</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.274</v>
+        <v>-0.1622</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6233</v>
+        <v>0.5308</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.982</v>
+        <v>-1.6776</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8254</v>
+        <v>-1.4901</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1566</v>
+        <v>-0.1875</v>
       </c>
       <c r="G19" t="n">
         <v>-2.4188</v>
@@ -1936,13 +1936,13 @@
         <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6731</v>
+        <v>-0.3686</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8904</v>
+        <v>-0.5552</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2174</v>
+        <v>0.1866</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1952</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.267</v>
+        <v>-1.7288</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8377</v>
+        <v>-0.726</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4293</v>
+        <v>-1.0029</v>
       </c>
       <c r="G20" t="n">
         <v>0.7746</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5191</v>
+        <v>-0.9809</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1524</v>
+        <v>-1.0407</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3666</v>
+        <v>0.0598</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4332</v>
+        <v>-2.4496</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.788</v>
+        <v>-2.3484</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6452</v>
+        <v>-0.1012</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7734</v>
+        <v>-2.8645</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2833</v>
+        <v>-0.8333</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4901</v>
+        <v>-2.0312</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3457</v>
+        <v>-1.9927</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8815</v>
+        <v>-1.3624</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2272</v>
+        <v>-0.6303</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.1191</v>
+        <v>-0.8718</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4018</v>
+        <v>0.5291</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.7173</v>
+        <v>-1.4009</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.029</v>
+        <v>-0.4551</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1538</v>
+        <v>-0.3557</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1248</v>
+        <v>-0.0994</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6743</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6538</v>
+        <v>-2.789</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4601</v>
+        <v>-2.5703</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1937</v>
+        <v>-0.2188</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.8645</v>
+        <v>-2.7734</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8333</v>
+        <v>-1.2833</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0312</v>
+        <v>-1.4901</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9927</v>
+        <v>0.3457</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3624</v>
+        <v>-0.8815</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6303</v>
+        <v>1.2272</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8718</v>
+        <v>-3.1191</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5291</v>
+        <v>-0.4018</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4009</v>
+        <v>-2.7173</v>
       </c>
       <c r="P22" t="n">
-        <v>0.87</v>
+        <v>-1.305</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6594</v>
+        <v>-0.3848</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4675</v>
+        <v>-0.9361</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1919</v>
+        <v>0.5513</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.6743</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.479</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>P. SCRUBB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3272</v>
+        <v>-2.9132</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3672</v>
+        <v>-0.5897</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.96</v>
+        <v>-2.3235</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8906</v>
+        <v>-2.4457</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9885</v>
+        <v>0.2644</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9021</v>
+        <v>-2.7101</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5573</v>
+        <v>0.7069</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6721</v>
+        <v>0.5506</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1147</v>
+        <v>0.1562</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3333</v>
+        <v>-3.1526</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3164</v>
+        <v>-0.2863</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.0169</v>
+        <v>-2.8663</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1061</v>
+        <v>-1.0776</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8099</v>
+        <v>-1.2966</v>
       </c>
       <c r="U23" t="n">
-        <v>0.916</v>
+        <v>0.219</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3423</v>
+        <v>-3.4787</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9378</v>
+        <v>-1.1437</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4045</v>
+        <v>-2.3349</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.3555</v>
+        <v>-2.8906</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1857</v>
+        <v>-0.9885</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1699</v>
+        <v>-1.9021</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1962</v>
+        <v>-0.5573</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0333</v>
+        <v>-0.6721</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2295</v>
+        <v>0.1147</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5517</v>
+        <v>-2.3333</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1523</v>
+        <v>-0.3164</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.3994</v>
+        <v>-2.0169</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3612</v>
+        <v>-0.0454</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9589</v>
+        <v>-0.5864</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3202</v>
+        <v>0.5411</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1745</v>
+        <v>-0.7602</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.1745</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. SCRUBB</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8599</v>
+        <v>-3.6621</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.925</v>
+        <v>-2.8261</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9349</v>
+        <v>-0.836</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4457</v>
+        <v>-2.3555</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2644</v>
+        <v>-0.1857</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.7101</v>
+        <v>-2.1699</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7069</v>
+        <v>0.1962</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5506</v>
+        <v>-0.0333</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1562</v>
+        <v>0.2295</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.1526</v>
+        <v>-2.5517</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2863</v>
+        <v>-0.1523</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.8663</v>
+        <v>-2.3994</v>
       </c>
       <c r="P25" t="n">
-        <v>1.7401</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R25" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.0243</v>
+        <v>0.0415</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.6319</v>
+        <v>-0.8472</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3924</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.13</v>
+        <v>0.1745</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.13</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.6246</v>
+        <v>-17.8795</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.2092</v>
+        <v>-10.2094</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.4153</v>
+        <v>-7.670100000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-15.0326</v>
@@ -2482,16 +2482,16 @@
         <v>11.9628</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.3778</v>
+        <v>-4.6324</v>
       </c>
       <c r="T26" t="n">
         <v>-7.5766</v>
       </c>
       <c r="U26" t="n">
-        <v>2.198900000000001</v>
+        <v>2.9442</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6981999999999999</v>
+        <v>0.6982</v>
       </c>
       <c r="W26" t="n">
         <v>4.910299999999999</v>
